--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104677_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104677_W25.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9383</v>
+        <v>3.3731</v>
       </c>
       <c r="E2" t="n">
-        <v>4.704</v>
+        <v>4.6655</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7657</v>
+        <v>-1.2924</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>1.5207</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.1039</v>
+        <v>1.9482</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5669</v>
+        <v>-0.4276</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6282</v>
+        <v>4.2453</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1354</v>
+        <v>4.0744</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7636</v>
+        <v>0.1708</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.1652</v>
+        <v>-2.7246</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9684</v>
+        <v>-2.1262</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1967</v>
+        <v>-0.5984</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5928</v>
+        <v>-0.6028</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.6692</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4506</v>
+        <v>0.0664</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8045</v>
+        <v>3.2381</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4072</v>
+        <v>4.9671</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6027</v>
+        <v>-1.729</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5391</v>
+        <v>0.4579</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9656</v>
+        <v>-2.1024</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4265</v>
+        <v>2.5604</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2883</v>
+        <v>3.597</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1072</v>
+        <v>-0.1486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1812</v>
+        <v>3.7456</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7493</v>
+        <v>-3.139</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1416</v>
+        <v>-1.9538</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6077</v>
+        <v>-1.1852</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1883</v>
+        <v>-0.2881</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2144</v>
+        <v>0.4509</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7514</v>
+        <v>0.2044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6794</v>
+        <v>0.598</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.3936</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3007</v>
+        <v>-1.2929</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5064</v>
+        <v>-0.5083</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7942</v>
+        <v>-0.7846</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1767</v>
+        <v>1.158</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9902</v>
+        <v>0.9718</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4774</v>
+        <v>-2.4508</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3205</v>
+        <v>0.7736</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1875</v>
+        <v>-0.2349</v>
       </c>
       <c r="U4" t="n">
-        <v>1.508</v>
+        <v>1.0085</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4507</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6384</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0526</v>
+        <v>0.1002</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0491</v>
+        <v>-0.0468</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6248</v>
+        <v>-0.6233</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5758</v>
+        <v>0.5765</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6185</v>
+        <v>1.6015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6675</v>
+        <v>-1.6483</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6666</v>
+        <v>-0.425</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U5" t="n">
-        <v>0.029</v>
+        <v>0.1535</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7572</v>
+        <v>-1.4361</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.95</v>
+        <v>-0.2717</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8072</v>
+        <v>-1.1644</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.662</v>
+        <v>-1.8284</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6754</v>
+        <v>-1.4367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0133</v>
+        <v>-0.3916</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4624</v>
+        <v>1.6265</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.5171</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4451</v>
+        <v>1.1094</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1245</v>
+        <v>-3.4549</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6927</v>
+        <v>-1.9538</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4318</v>
+        <v>-1.5011</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4146</v>
+        <v>-0.2208</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>-0.6902</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1364</v>
+        <v>0.4694</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2488</v>
+        <v>-1.6596</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.677</v>
+        <v>-0.8909</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5719</v>
+        <v>-0.7687</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8434</v>
+        <v>-0.6619</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4489</v>
+        <v>-0.6722</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3945</v>
+        <v>0.0103</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6363</v>
+        <v>0.4564</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5195</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1168</v>
+        <v>0.4392</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4797</v>
+        <v>-1.1184</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9684</v>
+        <v>-0.6895</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5113</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0198</v>
+        <v>-0.3148</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.113</v>
+        <v>-0.2091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0931</v>
+        <v>-0.1057</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6308</v>
+        <v>-2.5544</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1479</v>
+        <v>-1.0847</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.483</v>
+        <v>-1.4697</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6721</v>
+        <v>-1.6624</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8832</v>
+        <v>-0.8791</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7889</v>
+        <v>-0.7833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4037</v>
+        <v>0.402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0758</v>
+        <v>-2.0643</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2122</v>
+        <v>-1.2066</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7319</v>
+        <v>-0.6644</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.3485</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9261</v>
+        <v>-3.4194</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3171</v>
+        <v>-0.6269</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.609</v>
+        <v>-2.7925</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9524</v>
+        <v>-2.9414</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5557</v>
+        <v>-1.5457</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3967</v>
+        <v>-1.3957</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5772</v>
+        <v>1.5608</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.5296</v>
+        <v>-4.5023</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8025</v>
+        <v>-2.7868</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1098</v>
+        <v>-0.6145</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5353</v>
+        <v>-0.8204</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4255</v>
+        <v>0.2058</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8858</v>
+        <v>-3.4276</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3872</v>
+        <v>1.9441</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.273</v>
+        <v>-5.3718</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.9599</v>
+        <v>-4.9587</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1717</v>
+        <v>-2.1686</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7882</v>
+        <v>-2.7901</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4542</v>
+        <v>0.417</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0248</v>
+        <v>1.0062</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5706</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.4141</v>
+        <v>-5.3757</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.1965</v>
+        <v>-3.1748</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3776</v>
+        <v>-0.9258</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5303</v>
+        <v>-0.9203</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1527</v>
+        <v>-0.0055</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8988</v>
+        <v>-7.7155</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1199</v>
+        <v>-4.0425</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7789</v>
+        <v>-3.6731</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1527</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0678</v>
+        <v>-2.0652</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0849</v>
+        <v>-1.0875</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5021</v>
+        <v>-0.5295</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0835</v>
+        <v>-0.0969</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4186</v>
+        <v>-0.4326</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6506</v>
+        <v>-2.6232</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9843</v>
+        <v>-1.9683</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.0534</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5293</v>
+        <v>-0.3441</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3351</v>
+        <v>0.3975</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7959</v>
+        <v>-2.7951</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.5443</v>
+        <v>-13.8477</v>
       </c>
       <c r="E12" t="n">
-        <v>4.327500000000001</v>
+        <v>4.707100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.872</v>
+        <v>-18.555</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.5902</v>
+        <v>-14.5666</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.0722</v>
+        <v>-10.0533</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.5179</v>
+        <v>-4.513199999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>14.7434</v>
+        <v>14.535</v>
       </c>
       <c r="K12" t="n">
-        <v>8.666799999999999</v>
+        <v>8.550800000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>6.076600000000001</v>
+        <v>5.9842</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.3337</v>
+        <v>-29.1015</v>
       </c>
       <c r="N12" t="n">
-        <v>-18.739</v>
+        <v>-18.6041</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.5948</v>
+        <v>-10.4975</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1343</v>
+        <v>1.1383</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R12" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9165</v>
+        <v>-3.229200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.245300000000001</v>
+        <v>-5.5542</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3287</v>
+        <v>2.3249</v>
       </c>
       <c r="V12" t="n">
-        <v>2.8283</v>
+        <v>2.810099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>10.5735</v>
+        <v>10.5227</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.745200000000001</v>
+        <v>-7.7126</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1341</v>
+        <v>9.1121</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5876</v>
+        <v>8.529299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5466</v>
+        <v>0.5828</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8328</v>
+        <v>3.8136</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1718</v>
+        <v>3.1599</v>
       </c>
       <c r="I13" t="n">
-        <v>0.661</v>
+        <v>0.6536</v>
       </c>
       <c r="J13" t="n">
-        <v>6.353</v>
+        <v>6.3064</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4952</v>
+        <v>4.4676</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5202</v>
+        <v>-2.4929</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8892</v>
+        <v>0.892</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0907</v>
+        <v>0.0926</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7984</v>
+        <v>0.7994</v>
       </c>
       <c r="V13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.31</v>
+        <v>8.374499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9361</v>
+        <v>6.248</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3739</v>
+        <v>2.1265</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7126</v>
+        <v>5.7075</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0794</v>
+        <v>2.0712</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6331</v>
+        <v>3.6363</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9828</v>
+        <v>6.953</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2138</v>
+        <v>3.1921</v>
       </c>
       <c r="L14" t="n">
-        <v>3.769</v>
+        <v>3.7609</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2702</v>
+        <v>-1.2455</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9584</v>
+        <v>1.0328</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3758</v>
+        <v>1.0956</v>
       </c>
       <c r="V14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7206</v>
+        <v>2.4351</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1593</v>
+        <v>1.5978</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5613</v>
+        <v>0.8373</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5178</v>
+        <v>1.5031</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8542</v>
+        <v>0.8558</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6636</v>
+        <v>0.6473</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7804</v>
+        <v>2.7501</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7836</v>
+        <v>1.7754</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9967</v>
+        <v>0.9747</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2626</v>
+        <v>-1.2471</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4077</v>
+        <v>0.3159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4869</v>
+        <v>-0.0141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2145</v>
+        <v>1.9604</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3845</v>
+        <v>-0.0411</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5991</v>
+        <v>2.0015</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4394</v>
+        <v>0.4514</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6555</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1062</v>
+        <v>1.1068</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8887</v>
+        <v>0.8811</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4494</v>
+        <v>-0.4298</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.291</v>
+        <v>0.4392</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1518</v>
+        <v>0.2232</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9</v>
+        <v>1.207</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4475</v>
+        <v>0.5272</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4525</v>
+        <v>0.6798</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9986</v>
+        <v>2.9997</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2741</v>
+        <v>1.2779</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7246</v>
+        <v>1.7219</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6848</v>
+        <v>4.6597</v>
       </c>
       <c r="K17" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6068</v>
+        <v>2.5912</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6861</v>
+        <v>-1.6599</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4162</v>
+        <v>-0.1114</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4186</v>
+        <v>0.6066</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0885</v>
+        <v>0.1078</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3352</v>
+        <v>2.5411</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2467</v>
+        <v>-2.4334</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1616</v>
+        <v>-0.16</v>
       </c>
       <c r="H18" t="n">
-        <v>0.71</v>
+        <v>0.7067</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8716</v>
+        <v>-0.8667</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9645</v>
+        <v>1.9448</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4821</v>
+        <v>1.4684</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1261</v>
+        <v>-2.1048</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.114</v>
+        <v>0.1312</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0434</v>
+        <v>-0.8087</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1574</v>
+        <v>0.9399</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1275</v>
+        <v>-0.2529</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4203</v>
+        <v>-0.1481</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5478</v>
+        <v>-0.1048</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4086</v>
+        <v>0.9759</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5845</v>
+        <v>0.5111</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1759</v>
+        <v>0.4648</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7884</v>
+        <v>1.39</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0421</v>
+        <v>0.9136</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7463</v>
+        <v>0.4764</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3798</v>
+        <v>-0.4141</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4576</v>
+        <v>-0.4025</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9222</v>
+        <v>-0.0116</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9441</v>
+        <v>-0.2287</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8075</v>
+        <v>-0.5576</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1366</v>
+        <v>0.3289</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7997</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8924</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1996,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6002</v>
+        <v>-1.1957</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1297</v>
+        <v>0.5648</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4705</v>
+        <v>-1.7605</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9717</v>
+        <v>0.4081</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5079</v>
+        <v>0.5777</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4638</v>
+        <v>-0.1695</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4002</v>
+        <v>1.7682</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.0235</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4824</v>
+        <v>0.7447</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4285</v>
+        <v>-1.3601</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4099</v>
+        <v>-0.4458</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0186</v>
+        <v>-0.9143</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5719</v>
+        <v>0.871</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>-0.0166</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0154</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-1.792</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4617</v>
+        <v>-2.1853</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0305</v>
+        <v>1.6425</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4922</v>
+        <v>-3.8278</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2698</v>
+        <v>2.2678</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3017</v>
+        <v>2.2897</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0319</v>
+        <v>-0.0219</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8387</v>
+        <v>3.8147</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5775</v>
+        <v>3.554</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5689</v>
+        <v>-1.5469</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3858</v>
+        <v>0.6575</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>-0.0536</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0864</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-4.21</v>
+        <v>-4.2001</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.3707</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2609</v>
+        <v>-4.6459</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5304</v>
+        <v>-2.9068</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7304</v>
+        <v>-1.7392</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0264</v>
+        <v>-3.028</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7446</v>
+        <v>-0.7412</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2817</v>
+        <v>-2.2868</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3479</v>
+        <v>-1.3665</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2023</v>
+        <v>-1.2146</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6785</v>
+        <v>-1.6615</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3118</v>
+        <v>-0.0732</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0484</v>
+        <v>-0.4021</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3602</v>
+        <v>0.3289</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.5442</v>
+        <v>14.5447</v>
       </c>
       <c r="E24" t="n">
-        <v>18.8719</v>
+        <v>18.5547</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.327400000000001</v>
+        <v>-4.0102</v>
       </c>
       <c r="G24" t="n">
-        <v>14.5901</v>
+        <v>14.5667</v>
       </c>
       <c r="H24" t="n">
-        <v>10.0722</v>
+        <v>10.0533</v>
       </c>
       <c r="I24" t="n">
-        <v>4.518</v>
+        <v>4.513400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>29.3336</v>
+        <v>29.1015</v>
       </c>
       <c r="K24" t="n">
-        <v>18.7389</v>
+        <v>18.6041</v>
       </c>
       <c r="L24" t="n">
-        <v>10.5946</v>
+        <v>10.4973</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.7435</v>
+        <v>-14.535</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.666700000000001</v>
+        <v>-8.5509</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.076700000000001</v>
+        <v>-5.984300000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8784</v>
+        <v>-15.9344</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9165</v>
+        <v>3.9263</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.328800000000001</v>
+        <v>-2.3251</v>
       </c>
       <c r="U24" t="n">
-        <v>6.2454</v>
+        <v>6.2513</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8282</v>
+        <v>-2.809899999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>7.745200000000001</v>
+        <v>7.712700000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.5735</v>
+        <v>-10.5225</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104677_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104677_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.7126</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104677_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.5225</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
